--- a/docs/05_etc/スケジュール.xlsx
+++ b/docs/05_etc/スケジュール.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F0717BC-82C1-4B9E-BABE-76EC73375CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241600C3-B819-4FAE-AA0F-9AA576A9B7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{9D0A877E-512C-44A2-B45A-8469F978FA8B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{9D0A877E-512C-44A2-B45A-8469F978FA8B}"/>
   </bookViews>
   <sheets>
     <sheet name="作成テーブル" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="50">
   <si>
     <t>社員テーブル</t>
     <rPh sb="0" eb="2">
@@ -241,19 +241,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員登録機能テスト</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>部門登録機能実装</t>
     <rPh sb="0" eb="2">
       <t>ブモン</t>
@@ -270,19 +257,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門登録機能テスト</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>社員一覧表示機能実装</t>
     <rPh sb="0" eb="2">
       <t>シャイン</t>
@@ -302,22 +276,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員一覧登録機能テスト</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>イチラン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>部門登録機能実装</t>
     <rPh sb="0" eb="2">
       <t>ブモン</t>
@@ -361,19 +319,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員削除機能テスト</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>部門削除機能実装</t>
     <rPh sb="0" eb="2">
       <t>ブモン</t>
@@ -390,19 +335,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門削除機能テスト</t>
-    <rPh sb="0" eb="2">
-      <t>ブモン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>社員更新機能実装</t>
     <rPh sb="0" eb="2">
       <t>シャイン</t>
@@ -419,19 +351,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>社員更新機能テスト</t>
-    <rPh sb="0" eb="2">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>部門更新機能実装</t>
     <rPh sb="0" eb="2">
       <t>ブモン</t>
@@ -448,15 +367,259 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>部門更新機能テスト</t>
+    <t>図のレビュー</t>
+    <rPh sb="0" eb="1">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員登録機能テスト・レビュー</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門登録機能テスト・レビュー</t>
     <rPh sb="0" eb="2">
       <t>ブモン</t>
     </rPh>
     <rPh sb="2" eb="4">
-      <t>コウシン</t>
+      <t>トウロク</t>
     </rPh>
     <rPh sb="4" eb="6">
       <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員一覧登録機能テスト・レビュー</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員削除機能テスト・レビュー</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門削除機能テスト・レビュー</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員更新機能テスト・レビュー</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門更新機能テスト・レビュー</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>現状の不安要素</t>
+    <rPh sb="0" eb="2">
+      <t>ゲンジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="7">
+      <t>フアンヨウソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・シーケンス図想定より時間がかかりそう</t>
+    <rPh sb="6" eb="7">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ソウテイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・社員登録→部門登録の実装で変数名変更などでしくじらないように特に注意深く実装していく</t>
+    <rPh sb="1" eb="3">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヘンスウ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>トク</t>
+    </rPh>
+    <rPh sb="33" eb="36">
+      <t>チュウイブカ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・社員削除→練習での実装でなぜか削除する社員情報に部門データが入らない。どこでデータが欠落しているのかConsoleで出力しながら一つ一つ確認中。</t>
+    <rPh sb="1" eb="3">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>レンシュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>ハイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ケツラク</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>シュツリョク</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="71" eb="72">
+      <t>ナカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クラス図は正しいかは不安だが一通り作成。シーケンス図はどこからやってよいかがわからない状態。</t>
+    <rPh sb="3" eb="4">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>フアン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヒトトオ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ER図・クラス図はレビューをもとに修正まで終了。修正内容はコミット済み。</t>
+    <rPh sb="2" eb="3">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="24" eb="28">
+      <t>シュウセイナイヨウ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ズ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -571,7 +734,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -602,6 +765,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -609,12 +808,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1014,82 +1207,82 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="4"/>
-      <c r="B1" s="13">
+      <c r="B1" s="10">
         <v>46162</v>
       </c>
-      <c r="C1" s="13">
+      <c r="C1" s="10">
         <v>46163</v>
       </c>
-      <c r="D1" s="13">
+      <c r="D1" s="10">
         <v>46164</v>
       </c>
-      <c r="E1" s="13">
+      <c r="E1" s="10">
         <v>46167</v>
       </c>
-      <c r="F1" s="13">
+      <c r="F1" s="10">
         <v>46168</v>
       </c>
-      <c r="G1" s="13">
+      <c r="G1" s="10">
         <v>46169</v>
       </c>
-      <c r="H1" s="13">
+      <c r="H1" s="10">
         <v>46170</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5"/>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="6"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11" t="s">
+      <c r="A4" s="23"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="9"/>
@@ -1097,13 +1290,15 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="6"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
+      <c r="A5" s="23"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6" t="s">
+        <v>36</v>
+      </c>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
@@ -1111,8 +1306,8 @@
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="6"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -1121,8 +1316,8 @@
       <c r="H6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="6"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -1131,8 +1326,8 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="6"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -1141,8 +1336,8 @@
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="7"/>
-      <c r="B9" s="12"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -1151,23 +1346,23 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="F10" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>17</v>
@@ -1177,8 +1372,8 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="6"/>
-      <c r="B11" s="11" t="s">
+      <c r="A11" s="23"/>
+      <c r="B11" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="9"/>
@@ -1189,8 +1384,8 @@
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="6"/>
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="23"/>
+      <c r="B12" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="9"/>
@@ -1201,8 +1396,8 @@
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="6"/>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="23"/>
+      <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="9"/>
@@ -1213,8 +1408,8 @@
       <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="6"/>
-      <c r="B14" s="11"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -1223,8 +1418,8 @@
       <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="6"/>
-      <c r="B15" s="11"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
@@ -1233,8 +1428,8 @@
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="7"/>
-      <c r="B16" s="12"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
@@ -1254,7 +1449,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D39B20AA-3516-46A1-A5E7-2B2ADA44ACA3}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="5.75" customWidth="1"/>
@@ -1262,31 +1457,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="4"/>
-      <c r="B1" s="13">
+      <c r="A1" s="13"/>
+      <c r="B1" s="14">
         <v>46162</v>
       </c>
-      <c r="C1" s="13">
+      <c r="C1" s="14">
         <v>46163</v>
       </c>
-      <c r="D1" s="13">
+      <c r="D1" s="14">
         <v>46164</v>
       </c>
-      <c r="E1" s="13">
+      <c r="E1" s="14">
         <v>46167</v>
       </c>
-      <c r="F1" s="13">
+      <c r="F1" s="14">
         <v>46168</v>
       </c>
-      <c r="G1" s="13">
+      <c r="G1" s="14">
         <v>46169</v>
       </c>
-      <c r="H1" s="13">
+      <c r="H1" s="14">
         <v>46170</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="5"/>
+      <c r="A2" s="15"/>
       <c r="B2" s="12" t="s">
         <v>18</v>
       </c>
@@ -1309,196 +1504,225 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="14" t="s">
+    <row r="3" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="21"/>
+      <c r="B3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="19"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="19"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="6"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="6"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="6"/>
+      <c r="A6" s="19"/>
       <c r="B6" s="11"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="6" t="s">
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+    </row>
+    <row r="10" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="19" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="4" t="s">
+      <c r="D10" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="6"/>
-      <c r="B11" s="11" t="s">
+    <row r="11" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="19"/>
+      <c r="B11" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9" t="s">
+      <c r="C11" s="18"/>
+      <c r="D11" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="9"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="6"/>
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="19"/>
+      <c r="B12" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="6"/>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="19"/>
+      <c r="B13" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+    </row>
+    <row r="16" spans="1:8" ht="66" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="A10:A16"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
     <mergeCell ref="F7:F9"/>
     <mergeCell ref="G7:G9"/>
     <mergeCell ref="H7:H9"/>
@@ -1509,11 +1733,6 @@
     <mergeCell ref="F14:F16"/>
     <mergeCell ref="G14:G16"/>
     <mergeCell ref="H14:H16"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="A10:A16"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
     <mergeCell ref="E7:E9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
@@ -1532,102 +1751,104 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="4"/>
-      <c r="B1" s="13">
+      <c r="B1" s="10">
         <v>46162</v>
       </c>
-      <c r="C1" s="13">
+      <c r="C1" s="10">
         <v>46163</v>
       </c>
-      <c r="D1" s="13">
+      <c r="D1" s="10">
         <v>46164</v>
       </c>
-      <c r="E1" s="13">
+      <c r="E1" s="10">
         <v>46167</v>
       </c>
-      <c r="F1" s="13">
+      <c r="F1" s="10">
         <v>46168</v>
       </c>
-      <c r="G1" s="13">
+      <c r="G1" s="10">
         <v>46169</v>
       </c>
-      <c r="H1" s="13">
+      <c r="H1" s="10">
         <v>46170</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5"/>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="7" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="6"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11" t="s">
+      <c r="A4" s="23"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="9" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="23"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="6"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
@@ -1635,8 +1856,8 @@
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="6"/>
-      <c r="B6" s="11"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
@@ -1645,8 +1866,8 @@
       <c r="H6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="6"/>
-      <c r="B7" s="11"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="6"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -1655,8 +1876,8 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="6"/>
-      <c r="B8" s="11"/>
+      <c r="A8" s="23"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -1665,8 +1886,8 @@
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="7"/>
-      <c r="B9" s="12"/>
+      <c r="A9" s="24"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
@@ -1675,54 +1896,54 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="6"/>
-      <c r="B11" s="11" t="s">
+      <c r="A11" s="23"/>
+      <c r="B11" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="6"/>
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="23"/>
+      <c r="B12" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C12" s="9"/>
@@ -1733,8 +1954,8 @@
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="6"/>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="23"/>
+      <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C13" s="9"/>
@@ -1745,8 +1966,8 @@
       <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="6"/>
-      <c r="B14" s="11"/>
+      <c r="A14" s="23"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
@@ -1755,8 +1976,8 @@
       <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="6"/>
-      <c r="B15" s="11"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
@@ -1765,8 +1986,8 @@
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="7"/>
-      <c r="B16" s="12"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>

--- a/docs/05_etc/スケジュール.xlsx
+++ b/docs/05_etc/スケジュール.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241600C3-B819-4FAE-AA0F-9AA576A9B7A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E621DFC4-C936-4B8E-9CA6-93B3E4D2B74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{9D0A877E-512C-44A2-B45A-8469F978FA8B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="58">
   <si>
     <t>社員テーブル</t>
     <rPh sb="0" eb="2">
@@ -602,24 +602,195 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ER図・クラス図はレビューをもとに修正まで終了。修正内容はコミット済み。</t>
+    <t>追加でDB作成とアプリプロジェクトを作成して接続まで完了</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>セツゾク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テストでかなり苦戦中・UIテストはできたが、MSTestを用いたRepositoryのテストに時間がかかりそう。一方、Repositoryは毎回共通で使うので何回もテストする必要はなく、1回やったら何とかなりそう。</t>
+    <rPh sb="7" eb="9">
+      <t>クセン</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>イッポウ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>マイカイ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="75" eb="76">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>ナンカイ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="94" eb="95">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>ナン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員登録機能テスト（UIテスト完了、ホワイトボックスはRepositoryのみ）</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門登録機能テスト（UIテスト完了）</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門登録機能テスト（Reposioryのホワイトボックステスト）</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門一覧表示機能実装</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門一覧表示機能テスト・レビュー</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>イチランヒョウジ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機能等は先んじて実装できたが、夕方のレビューでテストの不備が見つかったので、来週はテストのやり直しからスタート予定。</t>
+    <rPh sb="0" eb="2">
+      <t>キノウ</t>
+    </rPh>
     <rPh sb="2" eb="3">
-      <t>ズ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ズ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ユウガタ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>フビ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ライシュウ</t>
+    </rPh>
+    <rPh sb="47" eb="48">
+      <t>ナオ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>ヨテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（当初の予定にはなかったが修正）
+ここまでのテストケースの書き方・テスト修正</t>
+    <rPh sb="1" eb="3">
+      <t>トウショ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
       <t>シュウセイ</t>
     </rPh>
-    <rPh sb="21" eb="23">
-      <t>シュウリョウ</t>
-    </rPh>
-    <rPh sb="24" eb="28">
-      <t>シュウセイナイヨウ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ズ</t>
+    <rPh sb="29" eb="30">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>シュウセイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -654,7 +825,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -664,6 +835,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,7 +911,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -792,13 +969,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1254,7 +1446,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="27" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -1280,7 +1472,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="23"/>
+      <c r="A4" s="28"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
         <v>25</v>
@@ -1294,7 +1486,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="23"/>
+      <c r="A5" s="28"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6" t="s">
         <v>36</v>
@@ -1306,7 +1498,7 @@
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="23"/>
+      <c r="A6" s="28"/>
       <c r="B6" s="6"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -1316,7 +1508,7 @@
       <c r="H6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="23"/>
+      <c r="A7" s="28"/>
       <c r="B7" s="6"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -1326,7 +1518,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="23"/>
+      <c r="A8" s="28"/>
       <c r="B8" s="6"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -1336,7 +1528,7 @@
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="24"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="7"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1346,7 +1538,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="28" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1372,7 +1564,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="23"/>
+      <c r="A11" s="28"/>
       <c r="B11" s="6" t="s">
         <v>23</v>
       </c>
@@ -1384,7 +1576,7 @@
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="23"/>
+      <c r="A12" s="28"/>
       <c r="B12" s="6" t="s">
         <v>21</v>
       </c>
@@ -1396,7 +1588,7 @@
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="23"/>
+      <c r="A13" s="28"/>
       <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
@@ -1408,7 +1600,7 @@
       <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="23"/>
+      <c r="A14" s="28"/>
       <c r="B14" s="6"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -1418,7 +1610,7 @@
       <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="23"/>
+      <c r="A15" s="28"/>
       <c r="B15" s="6"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -1428,7 +1620,7 @@
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="24"/>
+      <c r="A16" s="29"/>
       <c r="B16" s="7"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -1449,14 +1641,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D39B20AA-3516-46A1-A5E7-2B2ADA44ACA3}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="5.75" customWidth="1"/>
     <col min="2" max="8" width="23.33203125" customWidth="1"/>
+    <col min="11" max="17" width="25.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="13"/>
       <c r="B1" s="14">
         <v>46162</v>
@@ -1479,8 +1672,30 @@
       <c r="H1" s="14">
         <v>46170</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="J1" s="13"/>
+      <c r="K1" s="14">
+        <v>46162</v>
+      </c>
+      <c r="L1" s="14">
+        <v>46163</v>
+      </c>
+      <c r="M1" s="14">
+        <v>46164</v>
+      </c>
+      <c r="N1" s="14">
+        <v>46167</v>
+      </c>
+      <c r="O1" s="14">
+        <v>46168</v>
+      </c>
+      <c r="P1" s="14">
+        <v>46169</v>
+      </c>
+      <c r="Q1" s="14">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="15"/>
       <c r="B2" s="12" t="s">
         <v>18</v>
@@ -1503,19 +1718,41 @@
       <c r="H2" s="12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="21"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="24"/>
       <c r="B3" s="16" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="19" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="13" t="s">
@@ -1527,15 +1764,39 @@
       <c r="H3" s="13" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="19"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q3" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="25"/>
       <c r="B4" s="11"/>
       <c r="C4" s="17" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
+      <c r="E4" s="18" t="s">
+        <v>57</v>
+      </c>
       <c r="F4" s="18" t="s">
         <v>38</v>
       </c>
@@ -1543,9 +1804,25 @@
       <c r="H4" s="18" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="19"/>
+      <c r="J4" s="25"/>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="25"/>
       <c r="B5" s="11"/>
       <c r="C5" s="17" t="s">
         <v>36</v>
@@ -1555,9 +1832,21 @@
       <c r="F5" s="18"/>
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="19"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="M5" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="25"/>
       <c r="B6" s="11"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -1565,53 +1854,87 @@
       <c r="F6" s="18"/>
       <c r="G6" s="18"/>
       <c r="H6" s="18"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19" t="s">
+      <c r="J6" s="25"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="25"/>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-    </row>
-    <row r="10" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="19" t="s">
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="26"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+    </row>
+    <row r="10" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="19" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="13" t="s">
@@ -1623,14 +1946,40 @@
       <c r="H10" s="13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="19"/>
+      <c r="J10" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="O10" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q10" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="25"/>
       <c r="B11" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18" t="s">
+      <c r="C11" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="23" t="s">
         <v>38</v>
       </c>
       <c r="E11" s="18"/>
@@ -1639,62 +1988,130 @@
         <v>41</v>
       </c>
       <c r="H11" s="18"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="19"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q11" s="18"/>
+    </row>
+    <row r="12" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="25"/>
       <c r="B12" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25" t="s">
+        <v>56</v>
+      </c>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="19"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="25"/>
+      <c r="M12" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="25"/>
       <c r="B13" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19" t="s">
+      <c r="J13" s="25"/>
+      <c r="K13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="25"/>
+      <c r="M13" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18"/>
+    </row>
+    <row r="14" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="25"/>
+      <c r="B14" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-    </row>
-    <row r="16" spans="1:8" ht="66" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="25"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+    </row>
+    <row r="16" spans="1:17" ht="66" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
@@ -1717,23 +2134,39 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="32">
+    <mergeCell ref="O7:O9"/>
+    <mergeCell ref="P7:P9"/>
+    <mergeCell ref="Q7:Q9"/>
+    <mergeCell ref="J10:J16"/>
+    <mergeCell ref="L11:L16"/>
+    <mergeCell ref="K14:K16"/>
+    <mergeCell ref="M14:M16"/>
+    <mergeCell ref="N14:N16"/>
+    <mergeCell ref="O14:O16"/>
+    <mergeCell ref="P14:P16"/>
+    <mergeCell ref="Q14:Q16"/>
+    <mergeCell ref="J3:J9"/>
+    <mergeCell ref="K7:K9"/>
+    <mergeCell ref="L7:L9"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="E7:E9"/>
     <mergeCell ref="A3:A9"/>
     <mergeCell ref="A10:A16"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="D7:D9"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="C11:C16"/>
+    <mergeCell ref="D12:D16"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1798,7 +2231,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="27" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -1824,7 +2257,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="23"/>
+      <c r="A4" s="28"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
         <v>25</v>
@@ -1844,7 +2277,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="23"/>
+      <c r="A5" s="28"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6" t="s">
         <v>36</v>
@@ -1856,7 +2289,7 @@
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="23"/>
+      <c r="A6" s="28"/>
       <c r="B6" s="6"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -1866,7 +2299,7 @@
       <c r="H6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="23"/>
+      <c r="A7" s="28"/>
       <c r="B7" s="6"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -1876,7 +2309,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="23"/>
+      <c r="A8" s="28"/>
       <c r="B8" s="6"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -1886,7 +2319,7 @@
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="24"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="7"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1896,7 +2329,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="28" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1922,7 +2355,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="23"/>
+      <c r="A11" s="28"/>
       <c r="B11" s="6" t="s">
         <v>23</v>
       </c>
@@ -1942,7 +2375,7 @@
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="23"/>
+      <c r="A12" s="28"/>
       <c r="B12" s="6" t="s">
         <v>21</v>
       </c>
@@ -1954,7 +2387,7 @@
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="23"/>
+      <c r="A13" s="28"/>
       <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
@@ -1966,7 +2399,7 @@
       <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="23"/>
+      <c r="A14" s="28"/>
       <c r="B14" s="6"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -1976,7 +2409,7 @@
       <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="23"/>
+      <c r="A15" s="28"/>
       <c r="B15" s="6"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -1986,7 +2419,7 @@
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="24"/>
+      <c r="A16" s="29"/>
       <c r="B16" s="7"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>

--- a/docs/05_etc/スケジュール.xlsx
+++ b/docs/05_etc/スケジュール.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E621DFC4-C936-4B8E-9CA6-93B3E4D2B74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A08E581-A92E-4611-B509-095F76AB224C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{9D0A877E-512C-44A2-B45A-8469F978FA8B}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="65">
   <si>
     <t>社員テーブル</t>
     <rPh sb="0" eb="2">
@@ -791,6 +791,166 @@
     </rPh>
     <rPh sb="36" eb="38">
       <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追加：ホワイトボックステストの例外部分の検討
+→一度スキップ予定
+→やり方が見えてきたので明日再実装</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>レイガイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ケントウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>イチド</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>アシタ</t>
+    </rPh>
+    <rPh sb="47" eb="50">
+      <t>サイジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門削除機能実装（80%）</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誰も所属していない部門の削除はできたが、人がいる部門は削除できなかった。所属人数チェックメソッドを実装したので明日コントローラーに組み込みたい</t>
+    <rPh sb="0" eb="1">
+      <t>ダレ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショゾク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="36" eb="40">
+      <t>ショゾクニンズウ</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ジッソウ</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>アシタ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追記：部門の所属人数チェック実装</t>
+    <rPh sb="0" eb="2">
+      <t>ツイキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ショゾク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ニンズウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追記：テストコード大幅修正
+→削除機能までホワイトボックステスト</t>
+    <rPh sb="0" eb="2">
+      <t>ツイキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>オオハバ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="15" eb="19">
+      <t>サクジョキノウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>社員更新機能実装・テスト</t>
+    <rPh sb="0" eb="2">
+      <t>シャイン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部門更新機能実装・テスト</t>
+    <rPh sb="0" eb="2">
+      <t>ブモン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キノウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジッソウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -825,7 +985,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -841,6 +1001,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -911,7 +1083,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -960,18 +1132,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -981,16 +1144,28 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1001,6 +1176,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1446,7 +1624,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="28" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -1472,7 +1650,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="28"/>
+      <c r="A4" s="29"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
         <v>25</v>
@@ -1486,7 +1664,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="28"/>
+      <c r="A5" s="29"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6" t="s">
         <v>36</v>
@@ -1498,7 +1676,7 @@
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="28"/>
+      <c r="A6" s="29"/>
       <c r="B6" s="6"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -1508,7 +1686,7 @@
       <c r="H6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="28"/>
+      <c r="A7" s="29"/>
       <c r="B7" s="6"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -1518,7 +1696,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="28"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="6"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -1528,7 +1706,7 @@
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="29"/>
+      <c r="A9" s="30"/>
       <c r="B9" s="7"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -1538,7 +1716,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="29" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1564,7 +1742,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="28"/>
+      <c r="A11" s="29"/>
       <c r="B11" s="6" t="s">
         <v>23</v>
       </c>
@@ -1576,7 +1754,7 @@
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="28"/>
+      <c r="A12" s="29"/>
       <c r="B12" s="6" t="s">
         <v>21</v>
       </c>
@@ -1588,7 +1766,7 @@
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="28"/>
+      <c r="A13" s="29"/>
       <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
@@ -1600,7 +1778,7 @@
       <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="28"/>
+      <c r="A14" s="29"/>
       <c r="B14" s="6"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -1610,7 +1788,7 @@
       <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="28"/>
+      <c r="A15" s="29"/>
       <c r="B15" s="6"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -1620,7 +1798,7 @@
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="29"/>
+      <c r="A16" s="30"/>
       <c r="B16" s="7"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -1742,30 +1920,30 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="24"/>
-      <c r="B3" s="16" t="s">
+      <c r="A3" s="26"/>
+      <c r="B3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="22" t="s">
         <v>40</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="24"/>
-      <c r="K3" s="20" t="s">
+      <c r="J3" s="26"/>
+      <c r="K3" s="17" t="s">
         <v>19</v>
       </c>
       <c r="L3" s="11" t="s">
@@ -1774,7 +1952,7 @@
       <c r="M3" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="N3" s="21" t="s">
+      <c r="N3" s="18" t="s">
         <v>28</v>
       </c>
       <c r="O3" s="13" t="s">
@@ -1788,23 +1966,25 @@
       </c>
     </row>
     <row r="4" spans="1:17" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="25"/>
+      <c r="A4" s="24"/>
       <c r="B4" s="11"/>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18" t="s">
+      <c r="D4" s="16"/>
+      <c r="E4" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18" t="s">
+      <c r="G4" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="J4" s="25"/>
+      <c r="J4" s="24"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11" t="s">
         <v>25</v>
@@ -1812,27 +1992,29 @@
       <c r="M4" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18" t="s">
+      <c r="N4" s="16"/>
+      <c r="O4" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="18"/>
-      <c r="Q4" s="18" t="s">
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="25"/>
+      <c r="A5" s="24"/>
       <c r="B5" s="11"/>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="J5" s="25"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="J5" s="24"/>
       <c r="K5" s="11"/>
       <c r="L5" s="11" t="s">
         <v>36</v>
@@ -1840,113 +2022,113 @@
       <c r="M5" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="25"/>
+      <c r="A6" s="24"/>
       <c r="B6" s="11"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="J6" s="25"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="J6" s="24"/>
       <c r="K6" s="11"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25" t="s">
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25" t="s">
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="26"/>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="26"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
     </row>
     <row r="10" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="13" t="s">
-        <v>33</v>
+      <c r="G10" s="22" t="s">
+        <v>59</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="24" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="11" t="s">
@@ -1955,7 +2137,7 @@
       <c r="L10" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="M10" s="21" t="s">
+      <c r="M10" s="18" t="s">
         <v>27</v>
       </c>
       <c r="N10" s="13" t="s">
@@ -1971,147 +2153,155 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="25"/>
-      <c r="B11" s="17" t="s">
+    <row r="11" spans="1:17" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="24"/>
+      <c r="B11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="24" t="s">
         <v>50</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18" t="s">
+      <c r="E11" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="18"/>
-      <c r="J11" s="25"/>
+      <c r="H11" s="16"/>
+      <c r="J11" s="24"/>
       <c r="K11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="L11" s="25" t="s">
+      <c r="L11" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="M11" s="22" t="s">
+      <c r="M11" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18" t="s">
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="Q11" s="18"/>
+      <c r="Q11" s="16"/>
     </row>
     <row r="12" spans="1:17" ht="54" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="25"/>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="24"/>
+      <c r="B12" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25" t="s">
+      <c r="C12" s="24"/>
+      <c r="D12" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="J12" s="25"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="31" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="16"/>
+      <c r="J12" s="24"/>
       <c r="K12" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="L12" s="25"/>
-      <c r="M12" s="18" t="s">
+      <c r="L12" s="24"/>
+      <c r="M12" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="N12" s="18"/>
-      <c r="O12" s="18"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="18"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="25"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="24"/>
+      <c r="B13" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="J13" s="25"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="J13" s="24"/>
       <c r="K13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L13" s="25"/>
-      <c r="M13" s="18" t="s">
+      <c r="L13" s="24"/>
+      <c r="M13" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="18"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
     </row>
     <row r="14" spans="1:17" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25" t="s">
+      <c r="A14" s="24"/>
+      <c r="B14" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25" t="s">
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="L14" s="25"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
     </row>
     <row r="16" spans="1:17" ht="66" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="26"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="26"/>
-      <c r="Q16" s="26"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" t="s">
@@ -2134,7 +2324,24 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="33">
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="A10:A16"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="C11:C16"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="F7:F9"/>
+    <mergeCell ref="G7:G9"/>
+    <mergeCell ref="H7:H9"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E13:E16"/>
     <mergeCell ref="O7:O9"/>
     <mergeCell ref="P7:P9"/>
     <mergeCell ref="Q7:Q9"/>
@@ -2151,22 +2358,6 @@
     <mergeCell ref="L7:L9"/>
     <mergeCell ref="M7:M9"/>
     <mergeCell ref="N7:N9"/>
-    <mergeCell ref="F7:F9"/>
-    <mergeCell ref="G7:G9"/>
-    <mergeCell ref="H7:H9"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="A10:A16"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="C11:C16"/>
-    <mergeCell ref="D12:D16"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2231,7 +2422,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="28" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -2257,7 +2448,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="28"/>
+      <c r="A4" s="29"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6" t="s">
         <v>25</v>
@@ -2277,7 +2468,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="28"/>
+      <c r="A5" s="29"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6" t="s">
         <v>36</v>
@@ -2289,7 +2480,7 @@
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="28"/>
+      <c r="A6" s="29"/>
       <c r="B6" s="6"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -2299,7 +2490,7 @@
       <c r="H6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="28"/>
+      <c r="A7" s="29"/>
       <c r="B7" s="6"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -2309,7 +2500,7 @@
       <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="28"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="6"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -2319,7 +2510,7 @@
       <c r="H8" s="9"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="29"/>
+      <c r="A9" s="30"/>
       <c r="B9" s="7"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -2329,7 +2520,7 @@
       <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="29" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -2355,7 +2546,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="28"/>
+      <c r="A11" s="29"/>
       <c r="B11" s="6" t="s">
         <v>23</v>
       </c>
@@ -2375,7 +2566,7 @@
       <c r="H11" s="9"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="28"/>
+      <c r="A12" s="29"/>
       <c r="B12" s="6" t="s">
         <v>21</v>
       </c>
@@ -2387,7 +2578,7 @@
       <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="28"/>
+      <c r="A13" s="29"/>
       <c r="B13" s="6" t="s">
         <v>22</v>
       </c>
@@ -2399,7 +2590,7 @@
       <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="28"/>
+      <c r="A14" s="29"/>
       <c r="B14" s="6"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -2409,7 +2600,7 @@
       <c r="H14" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="28"/>
+      <c r="A15" s="29"/>
       <c r="B15" s="6"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -2419,7 +2610,7 @@
       <c r="H15" s="9"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="29"/>
+      <c r="A16" s="30"/>
       <c r="B16" s="7"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
